--- a/Scripts_&_data/All_the_figures_&_SI/Table_S2.xlsx
+++ b/Scripts_&_data/All_the_figures_&_SI/Table_S2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simondellicour/Dropbox/Temp_MBP4/BEES/SDM_Bombus_sp_3/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simondellicour/Dropbox/Simon_repos/Files/Publications/B4_De_Tandt_et_al_counterclim_Bombus/2° submission (NCC)/Submit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F303FF5D-8C01-9340-8CD7-99FFED32490C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB4DEC52-1FC7-1646-9FE2-2D652CE1D490}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="1260" windowWidth="28040" windowHeight="17420" xr2:uid="{6EBB44D6-8252-444B-999D-F1993466DA6E}"/>
+    <workbookView xWindow="12360" yWindow="-20420" windowWidth="28040" windowHeight="17420" xr2:uid="{6EBB44D6-8252-444B-999D-F1993466DA6E}"/>
   </bookViews>
   <sheets>
     <sheet name="Table S2" sheetId="1" r:id="rId1"/>
@@ -370,8 +370,332 @@
     <t>0.224</t>
   </si>
   <si>
+    <t>&gt;0.999</t>
+  </si>
+  <si>
+    <t>0.999</t>
+  </si>
+  <si>
+    <t>0.990</t>
+  </si>
+  <si>
+    <t>0.864</t>
+  </si>
+  <si>
+    <t>0.517</t>
+  </si>
+  <si>
+    <t>0.866</t>
+  </si>
+  <si>
+    <t>0.709</t>
+  </si>
+  <si>
+    <t>0.204</t>
+  </si>
+  <si>
+    <t>0.027</t>
+  </si>
+  <si>
+    <t>0.996</t>
+  </si>
+  <si>
+    <t>0.039</t>
+  </si>
+  <si>
+    <t>0.988</t>
+  </si>
+  <si>
+    <t>0.593</t>
+  </si>
+  <si>
+    <t>0.932</t>
+  </si>
+  <si>
+    <t>0.916</t>
+  </si>
+  <si>
+    <t>0.817</t>
+  </si>
+  <si>
+    <t>0.982</t>
+  </si>
+  <si>
+    <t>0.981</t>
+  </si>
+  <si>
+    <t>0.475</t>
+  </si>
+  <si>
+    <t>0.451</t>
+  </si>
+  <si>
+    <t>0.942</t>
+  </si>
+  <si>
+    <t>0.822</t>
+  </si>
+  <si>
+    <t>0.027*</t>
+  </si>
+  <si>
+    <t>0.199</t>
+  </si>
+  <si>
+    <t>0.574</t>
+  </si>
+  <si>
+    <t>0.687</t>
+  </si>
+  <si>
+    <t>0.012*</t>
+  </si>
+  <si>
+    <t>0.239</t>
+  </si>
+  <si>
+    <t>0.973</t>
+  </si>
+  <si>
+    <t>0.332</t>
+  </si>
+  <si>
+    <t>0.945</t>
+  </si>
+  <si>
+    <t>0.900</t>
+  </si>
+  <si>
+    <t>0.302</t>
+  </si>
+  <si>
+    <t>0.536</t>
+  </si>
+  <si>
+    <t>0.192</t>
+  </si>
+  <si>
+    <t>0.156</t>
+  </si>
+  <si>
+    <t>0.043</t>
+  </si>
+  <si>
+    <t>0.885</t>
+  </si>
+  <si>
+    <t>0.998</t>
+  </si>
+  <si>
+    <t>0.524</t>
+  </si>
+  <si>
+    <t>0.343</t>
+  </si>
+  <si>
+    <t>0.172</t>
+  </si>
+  <si>
+    <t>0.479</t>
+  </si>
+  <si>
+    <t>0.662</t>
+  </si>
+  <si>
+    <t>0.985</t>
+  </si>
+  <si>
+    <t>0.473</t>
+  </si>
+  <si>
+    <t>0.035</t>
+  </si>
+  <si>
+    <t>0.995</t>
+  </si>
+  <si>
+    <t>0.762</t>
+  </si>
+  <si>
+    <t>0.175</t>
+  </si>
+  <si>
+    <t>0.255</t>
+  </si>
+  <si>
+    <t>0.016*</t>
+  </si>
+  <si>
+    <t>0.939</t>
+  </si>
+  <si>
+    <t>0.400</t>
+  </si>
+  <si>
+    <t>0.786</t>
+  </si>
+  <si>
+    <t>0.889</t>
+  </si>
+  <si>
+    <t>0.010</t>
+  </si>
+  <si>
+    <t>0.137</t>
+  </si>
+  <si>
+    <t>0.484</t>
+  </si>
+  <si>
+    <t>0.997</t>
+  </si>
+  <si>
+    <t>0.134</t>
+  </si>
+  <si>
+    <t>0.992</t>
+  </si>
+  <si>
+    <t>0.292</t>
+  </si>
+  <si>
+    <t>0.797</t>
+  </si>
+  <si>
+    <t>0.961</t>
+  </si>
+  <si>
+    <t>0.012</t>
+  </si>
+  <si>
+    <t>0.993</t>
+  </si>
+  <si>
+    <t>0.994</t>
+  </si>
+  <si>
+    <t>0.184</t>
+  </si>
+  <si>
+    <t>0.018</t>
+  </si>
+  <si>
+    <t>0.019</t>
+  </si>
+  <si>
+    <t>0.527</t>
+  </si>
+  <si>
+    <t>0.550</t>
+  </si>
+  <si>
+    <t>0.059</t>
+  </si>
+  <si>
+    <t>0.179</t>
+  </si>
+  <si>
+    <t>0.974</t>
+  </si>
+  <si>
+    <t>0.802</t>
+  </si>
+  <si>
+    <t>0.427</t>
+  </si>
+  <si>
+    <t>0.315</t>
+  </si>
+  <si>
+    <t>0.977</t>
+  </si>
+  <si>
+    <t>0.669</t>
+  </si>
+  <si>
+    <t>0.056</t>
+  </si>
+  <si>
+    <t>0.101</t>
+  </si>
+  <si>
+    <t>0.699</t>
+  </si>
+  <si>
+    <t>0.465</t>
+  </si>
+  <si>
+    <t>0.809</t>
+  </si>
+  <si>
+    <t>0.845</t>
+  </si>
+  <si>
+    <t>0.958</t>
+  </si>
+  <si>
+    <t>0.115</t>
+  </si>
+  <si>
+    <t>0.477</t>
+  </si>
+  <si>
+    <t>0.658</t>
+  </si>
+  <si>
+    <t>0.829</t>
+  </si>
+  <si>
+    <t>0.523</t>
+  </si>
+  <si>
+    <t>0.339</t>
+  </si>
+  <si>
+    <t>0.015</t>
+  </si>
+  <si>
+    <t>0.989</t>
+  </si>
+  <si>
+    <t>0.986</t>
+  </si>
+  <si>
+    <t>0.528</t>
+  </si>
+  <si>
+    <t>0.966</t>
+  </si>
+  <si>
+    <t>0.005*</t>
+  </si>
+  <si>
+    <t>0.633</t>
+  </si>
+  <si>
+    <t>0.826</t>
+  </si>
+  <si>
+    <t>0.746</t>
+  </si>
+  <si>
+    <t>0.984</t>
+  </si>
+  <si>
+    <t>0.062</t>
+  </si>
+  <si>
+    <t>0.601</t>
+  </si>
+  <si>
+    <t>0.215</t>
+  </si>
+  <si>
+    <t>0.112</t>
+  </si>
+  <si>
     <r>
-      <t xml:space="preserve">Wilcoxon-Mann-Witheney test p-values for BI </t>
+      <t xml:space="preserve">Wilcoxon-Mann-Whiteney test p-values for BI </t>
     </r>
     <r>
       <rPr>
@@ -397,7 +721,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Wilcoxon-Mann-Witheney test p-values for BI </t>
+      <t xml:space="preserve">Wilcoxon-Mann-Whiteney test p-values for BI </t>
     </r>
     <r>
       <rPr>
@@ -423,7 +747,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Wilcoxon-Mann-Witheney test p-values for BI </t>
+      <t xml:space="preserve">Wilcoxon-Mann-Whiteney test p-values for BI </t>
     </r>
     <r>
       <rPr>
@@ -446,330 +770,6 @@
       </rPr>
       <t xml:space="preserve"> than zero</t>
     </r>
-  </si>
-  <si>
-    <t>&gt;0.999</t>
-  </si>
-  <si>
-    <t>0.999</t>
-  </si>
-  <si>
-    <t>0.990</t>
-  </si>
-  <si>
-    <t>0.864</t>
-  </si>
-  <si>
-    <t>0.517</t>
-  </si>
-  <si>
-    <t>0.866</t>
-  </si>
-  <si>
-    <t>0.709</t>
-  </si>
-  <si>
-    <t>0.204</t>
-  </si>
-  <si>
-    <t>0.027</t>
-  </si>
-  <si>
-    <t>0.996</t>
-  </si>
-  <si>
-    <t>0.039</t>
-  </si>
-  <si>
-    <t>0.988</t>
-  </si>
-  <si>
-    <t>0.593</t>
-  </si>
-  <si>
-    <t>0.932</t>
-  </si>
-  <si>
-    <t>0.916</t>
-  </si>
-  <si>
-    <t>0.817</t>
-  </si>
-  <si>
-    <t>0.982</t>
-  </si>
-  <si>
-    <t>0.981</t>
-  </si>
-  <si>
-    <t>0.475</t>
-  </si>
-  <si>
-    <t>0.451</t>
-  </si>
-  <si>
-    <t>0.942</t>
-  </si>
-  <si>
-    <t>0.822</t>
-  </si>
-  <si>
-    <t>0.027*</t>
-  </si>
-  <si>
-    <t>0.199</t>
-  </si>
-  <si>
-    <t>0.574</t>
-  </si>
-  <si>
-    <t>0.687</t>
-  </si>
-  <si>
-    <t>0.012*</t>
-  </si>
-  <si>
-    <t>0.239</t>
-  </si>
-  <si>
-    <t>0.973</t>
-  </si>
-  <si>
-    <t>0.332</t>
-  </si>
-  <si>
-    <t>0.945</t>
-  </si>
-  <si>
-    <t>0.900</t>
-  </si>
-  <si>
-    <t>0.302</t>
-  </si>
-  <si>
-    <t>0.536</t>
-  </si>
-  <si>
-    <t>0.192</t>
-  </si>
-  <si>
-    <t>0.156</t>
-  </si>
-  <si>
-    <t>0.043</t>
-  </si>
-  <si>
-    <t>0.885</t>
-  </si>
-  <si>
-    <t>0.998</t>
-  </si>
-  <si>
-    <t>0.524</t>
-  </si>
-  <si>
-    <t>0.343</t>
-  </si>
-  <si>
-    <t>0.172</t>
-  </si>
-  <si>
-    <t>0.479</t>
-  </si>
-  <si>
-    <t>0.662</t>
-  </si>
-  <si>
-    <t>0.985</t>
-  </si>
-  <si>
-    <t>0.473</t>
-  </si>
-  <si>
-    <t>0.035</t>
-  </si>
-  <si>
-    <t>0.995</t>
-  </si>
-  <si>
-    <t>0.762</t>
-  </si>
-  <si>
-    <t>0.175</t>
-  </si>
-  <si>
-    <t>0.255</t>
-  </si>
-  <si>
-    <t>0.016*</t>
-  </si>
-  <si>
-    <t>0.939</t>
-  </si>
-  <si>
-    <t>0.400</t>
-  </si>
-  <si>
-    <t>0.786</t>
-  </si>
-  <si>
-    <t>0.889</t>
-  </si>
-  <si>
-    <t>0.010</t>
-  </si>
-  <si>
-    <t>0.137</t>
-  </si>
-  <si>
-    <t>0.484</t>
-  </si>
-  <si>
-    <t>0.997</t>
-  </si>
-  <si>
-    <t>0.134</t>
-  </si>
-  <si>
-    <t>0.992</t>
-  </si>
-  <si>
-    <t>0.292</t>
-  </si>
-  <si>
-    <t>0.797</t>
-  </si>
-  <si>
-    <t>0.961</t>
-  </si>
-  <si>
-    <t>0.012</t>
-  </si>
-  <si>
-    <t>0.993</t>
-  </si>
-  <si>
-    <t>0.994</t>
-  </si>
-  <si>
-    <t>0.184</t>
-  </si>
-  <si>
-    <t>0.018</t>
-  </si>
-  <si>
-    <t>0.019</t>
-  </si>
-  <si>
-    <t>0.527</t>
-  </si>
-  <si>
-    <t>0.550</t>
-  </si>
-  <si>
-    <t>0.059</t>
-  </si>
-  <si>
-    <t>0.179</t>
-  </si>
-  <si>
-    <t>0.974</t>
-  </si>
-  <si>
-    <t>0.802</t>
-  </si>
-  <si>
-    <t>0.427</t>
-  </si>
-  <si>
-    <t>0.315</t>
-  </si>
-  <si>
-    <t>0.977</t>
-  </si>
-  <si>
-    <t>0.669</t>
-  </si>
-  <si>
-    <t>0.056</t>
-  </si>
-  <si>
-    <t>0.101</t>
-  </si>
-  <si>
-    <t>0.699</t>
-  </si>
-  <si>
-    <t>0.465</t>
-  </si>
-  <si>
-    <t>0.809</t>
-  </si>
-  <si>
-    <t>0.845</t>
-  </si>
-  <si>
-    <t>0.958</t>
-  </si>
-  <si>
-    <t>0.115</t>
-  </si>
-  <si>
-    <t>0.477</t>
-  </si>
-  <si>
-    <t>0.658</t>
-  </si>
-  <si>
-    <t>0.829</t>
-  </si>
-  <si>
-    <t>0.523</t>
-  </si>
-  <si>
-    <t>0.339</t>
-  </si>
-  <si>
-    <t>0.015</t>
-  </si>
-  <si>
-    <t>0.989</t>
-  </si>
-  <si>
-    <t>0.986</t>
-  </si>
-  <si>
-    <t>0.528</t>
-  </si>
-  <si>
-    <t>0.966</t>
-  </si>
-  <si>
-    <t>0.005*</t>
-  </si>
-  <si>
-    <t>0.633</t>
-  </si>
-  <si>
-    <t>0.826</t>
-  </si>
-  <si>
-    <t>0.746</t>
-  </si>
-  <si>
-    <t>0.984</t>
-  </si>
-  <si>
-    <t>0.062</t>
-  </si>
-  <si>
-    <t>0.601</t>
-  </si>
-  <si>
-    <t>0.215</t>
-  </si>
-  <si>
-    <t>0.112</t>
   </si>
 </sst>
 </file>
@@ -1681,19 +1681,19 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B1" s="6" t="s">
-        <v>116</v>
+        <v>224</v>
       </c>
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
       <c r="F1" s="6" t="s">
-        <v>117</v>
+        <v>225</v>
       </c>
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
       <c r="I1" s="6"/>
       <c r="J1" s="6" t="s">
-        <v>118</v>
+        <v>226</v>
       </c>
       <c r="K1" s="6"/>
       <c r="L1" s="6"/>
@@ -1754,16 +1754,16 @@
         <v>53</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>51</v>
@@ -1775,7 +1775,7 @@
         <v>51</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
@@ -1798,7 +1798,7 @@
         <v>51</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>51</v>
@@ -1807,16 +1807,16 @@
         <v>51</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
@@ -1839,25 +1839,25 @@
         <v>71</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>52</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>51</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
@@ -1877,28 +1877,28 @@
         <v>61</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>63</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="J6" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="M6" s="2" t="s">
         <v>179</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
@@ -1921,7 +1921,7 @@
         <v>51</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>51</v>
@@ -1930,16 +1930,16 @@
         <v>51</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
@@ -1971,16 +1971,16 @@
         <v>51</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
@@ -2000,16 +2000,16 @@
         <v>63</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>51</v>
@@ -2053,16 +2053,16 @@
         <v>51</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
@@ -2082,19 +2082,19 @@
         <v>65</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>51</v>
@@ -2103,7 +2103,7 @@
         <v>51</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
@@ -2126,16 +2126,16 @@
         <v>95</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>79</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>51</v>
@@ -2144,7 +2144,7 @@
         <v>61</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
@@ -2167,7 +2167,7 @@
         <v>51</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>57</v>
@@ -2176,16 +2176,16 @@
         <v>51</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>106</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
@@ -2205,16 +2205,16 @@
         <v>73</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>94</v>
@@ -2223,10 +2223,10 @@
         <v>55</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
@@ -2249,16 +2249,16 @@
         <v>51</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>51</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>55</v>
@@ -2267,7 +2267,7 @@
         <v>51</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
@@ -2287,28 +2287,28 @@
         <v>76</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>55</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
@@ -2340,16 +2340,16 @@
         <v>51</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
@@ -2369,19 +2369,19 @@
         <v>51</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>51</v>
@@ -2410,28 +2410,28 @@
         <v>81</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>71</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
@@ -2451,16 +2451,16 @@
         <v>51</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>51</v>
@@ -2492,28 +2492,28 @@
         <v>84</v>
       </c>
       <c r="F21" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="G21" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>146</v>
-      </c>
       <c r="J21" s="2" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
@@ -2536,16 +2536,16 @@
         <v>111</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>51</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>51</v>
@@ -2554,7 +2554,7 @@
         <v>51</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
@@ -2574,25 +2574,25 @@
         <v>51</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>79</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>51</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="M23" s="2" t="s">
         <v>51</v>
@@ -2618,25 +2618,25 @@
         <v>51</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
@@ -2656,28 +2656,28 @@
         <v>92</v>
       </c>
       <c r="F25" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="G25" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>154</v>
-      </c>
       <c r="J25" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="M25" s="2" t="s">
         <v>202</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="L25" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="M25" s="2" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
@@ -2709,16 +2709,16 @@
         <v>51</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
@@ -2750,16 +2750,16 @@
         <v>51</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
@@ -2782,7 +2782,7 @@
         <v>51</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>71</v>
@@ -2791,16 +2791,16 @@
         <v>52</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
@@ -2832,16 +2832,16 @@
         <v>51</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
@@ -2873,16 +2873,16 @@
         <v>51</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
@@ -2902,28 +2902,28 @@
         <v>98</v>
       </c>
       <c r="F31" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="I31" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="G31" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>159</v>
-      </c>
       <c r="J31" s="2" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>71</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
@@ -2946,7 +2946,7 @@
         <v>51</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>51</v>
@@ -2955,16 +2955,16 @@
         <v>51</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.2">
@@ -2984,28 +2984,28 @@
         <v>102</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>51</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.2">
@@ -3031,22 +3031,22 @@
         <v>66</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>51</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.2">
@@ -3066,28 +3066,28 @@
         <v>107</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>72</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>51</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.2">
@@ -3107,28 +3107,28 @@
         <v>110</v>
       </c>
       <c r="F36" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="I36" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="G36" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>170</v>
-      </c>
       <c r="J36" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.2">
@@ -3160,16 +3160,16 @@
         <v>51</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.2">
@@ -3201,16 +3201,16 @@
         <v>51</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.2">
@@ -3242,16 +3242,16 @@
         <v>51</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.2">
@@ -3283,16 +3283,16 @@
         <v>51</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.2">
@@ -3324,16 +3324,16 @@
         <v>51</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.2">
@@ -3365,16 +3365,16 @@
         <v>51</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.2">
@@ -3394,28 +3394,28 @@
         <v>113</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>51</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.2">
@@ -3447,16 +3447,16 @@
         <v>51</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.2">
@@ -3479,7 +3479,7 @@
         <v>51</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>51</v>
@@ -3488,16 +3488,16 @@
         <v>51</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.2">
@@ -3520,7 +3520,7 @@
         <v>51</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>51</v>
@@ -3529,16 +3529,16 @@
         <v>51</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.2">
@@ -3570,16 +3570,16 @@
         <v>51</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.2">
@@ -3611,16 +3611,16 @@
         <v>51</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.2">
@@ -3652,16 +3652,16 @@
         <v>51</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/Scripts_&_data/All_the_figures_&_SI/Table_S2.xlsx
+++ b/Scripts_&_data/All_the_figures_&_SI/Table_S2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simondellicour/Dropbox/Simon_repos/Files/Publications/B4_De_Tandt_et_al_counterclim_Bombus/2° submission (NCC)/Submit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB4DEC52-1FC7-1646-9FE2-2D652CE1D490}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44C05873-1C01-444A-A35A-EE34B159BC89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12360" yWindow="-20420" windowWidth="28040" windowHeight="17420" xr2:uid="{6EBB44D6-8252-444B-999D-F1993466DA6E}"/>
   </bookViews>
@@ -732,7 +732,7 @@
         <rFont val="Aptos Narrow"/>
         <scheme val="minor"/>
       </rPr>
-      <t>higher</t>
+      <t>greater</t>
     </r>
     <r>
       <rPr>
@@ -758,7 +758,7 @@
         <rFont val="Aptos Narrow"/>
         <scheme val="minor"/>
       </rPr>
-      <t>lower</t>
+      <t>less</t>
     </r>
     <r>
       <rPr>
